--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_arica_y_parinacota.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:35</t>
+    <t xml:space="preserve">2026-09-24 01:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -577,7 +577,7 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.22</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.29</v>
       </c>
       <c r="G3" s="2"/>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.25</v>
       </c>
       <c r="G4" s="2"/>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G5" s="2"/>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="G6" s="2"/>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G10" s="2"/>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="G14" s="2"/>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="G15" s="2"/>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="G19" s="2"/>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="G20" s="2"/>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.17</v>
       </c>
       <c r="G21" s="2"/>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
       <c r="G22" s="2"/>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="G24" s="2"/>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="n">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
       <c r="G25" s="2"/>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.27</v>
       </c>
       <c r="G26" s="2"/>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="G27" s="2"/>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="G28" s="2"/>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="G30" s="2"/>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="G34" s="2"/>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G36" s="2"/>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2"/>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="G43" s="2"/>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="G44" s="2"/>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="G45" s="2"/>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.18</v>
       </c>
       <c r="G65" s="2"/>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="G66" s="2"/>
     </row>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="G67" s="2"/>
     </row>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:25</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2022_arica_y_parinacota.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 19:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
